--- a/Data/Happy Town Material Expense.xlsx
+++ b/Data/Happy Town Material Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d772b42a7a1256b2/Desktop/Business/TSK Constructions/Projects/Building Construction/Happy Town - Sulur/Accounts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="386" documentId="13_ncr:1_{FE593903-E758-44D3-AFD8-C796D57071E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEA055B7-9589-41A5-8BC5-1F6FA84ED413}"/>
+  <xr:revisionPtr revIDLastSave="392" documentId="13_ncr:1_{FE593903-E758-44D3-AFD8-C796D57071E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFB026CC-FE57-45C4-8DA4-BF3D88313889}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="83">
   <si>
     <t>DATE</t>
   </si>
@@ -449,7 +449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -479,6 +479,7 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -3390,11 +3391,11 @@
       </c>
       <c r="C2" s="7">
         <f>SUMIF('Payment Details'!B2:B1000,'Vendor Balance Sheet'!A2,'Payment Details'!C2:C1000)</f>
-        <v>700000</v>
+        <v>725000</v>
       </c>
       <c r="D2" s="7">
         <f>B2-C2</f>
-        <v>28800</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -3562,7 +3563,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B843CC5F-739E-45E9-AC65-8442CF552E38}">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="3"/>
@@ -4513,6 +4514,26 @@
         <v>41</v>
       </c>
     </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="3">
+        <v>46172</v>
+      </c>
+      <c r="B48" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="4">
+        <v>25000</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F48" s="22" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F24" xr:uid="{B843CC5F-739E-45E9-AC65-8442CF552E38}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
